--- a/reviews/zero-day-unsup-drl-cl-xai/systematic_review.xlsx
+++ b/reviews/zero-day-unsup-drl-cl-xai/systematic_review.xlsx
@@ -8,17 +8,21 @@
   </bookViews>
   <sheets>
     <sheet name="Protocol" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Search Log" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="PRISMA" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Extraction" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Summary" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Quality" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Gap Matrix" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Opportunities" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Excluded" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="References" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Gap Duplication Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="All Papers - Gap Test" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Search Log" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="PRISMA" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Extraction" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Summary" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Quality" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Gap Matrix" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Opportunities" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Excluded" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="References" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Papers - Gap Test'!$A$1:$T$64</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -26,7 +30,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -38,8 +42,11 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -49,6 +56,31 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE699"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8CBAD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FF7C80"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -64,7 +96,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -72,6 +104,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -735,6 +784,1126 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Research direction</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Addresses gaps</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Motivating papers</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Explanation-gated pseudo-labelling: admit an auto-labelled zero-day sample to retraining only when its attribution profile (SHAP on the autoencoder's reconstruction error, as in Antwarg et al.) agrees with its cluster's profile; report pseudo-label precision.</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Explainability, Label, Method</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>1, 8, 18, 20</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Explanation-aware DRL controller: add attribution-shift features to the agent's state and give it skip / rollback actions, so each retraining decision is justified and harmful updates are vetoed.</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>DRL decision scope, Explainability</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>1, 4, 5, 9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Explaining continual updates: compare classifier attributions before and after each update to detect forgetting or shortcut learning, and expose it to analysts.</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Explainability, Real-world</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>1, 13, 14</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Novelty-preserving encoding for zero-day ransomware: study categorical encoding (one-hot, embeddings) as a design factor for unsupervised detection, using UGRansome and NetFlow.</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Data / feature representation, Generalization</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2, 22</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>A shared zero-day continual-learning benchmark protocol: listed held-out families or classes, cross-dataset streams, pseudo-label metrics, multiple seeds, released code.</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Generalization, Statistics / reproducibility</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>1, 2, 5, 8</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="50" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Venue</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Quartile</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Stage</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>SOUL: Semi-supervised Open-world continUal Learning for NIDS (arXiv 2412.00911)</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Venue type</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>preprint only, no journal version found</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>CITADEL: Continual Anomaly Detection for IoT Intrusion Detection (arXiv 2508.19450)</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Venue type</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>preprint only, no journal version found</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>ACORN-IDS: Adaptive Continual Novelty Detection for IDS (arXiv 2602.07291)</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Venue type</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>preprint only, no journal version found</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>ThreatFormer-IDS: Zero-Day Generalization and Explainable Attribution (arXiv 2603.00185)</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Venue type</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>preprint only, no journal version found</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>DeepXplain: XAI-Guided Autonomous Defense Against Multi-Stage APT (arXiv 2603.21296)</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Venue type</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>preprint only, no journal version found</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>UNAD+: Explainable Hybrid Framework for Unknown Network Attack Detection (arXiv 2605.22621)</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Venue type</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>preprint only, no journal version found</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Navigating the Latent Manifold: Proactive Concept Drift Adaptation for NIDS (arXiv 2609.08623)</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Venue type</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>preprint only, no journal version found</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Enhancing Autonomous Online IDS for IoT with Reliable Pseudo-Labels (arXiv 2605.26166)</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Venue type</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>preprint only, no journal version found</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Probabilistic Robustness-driven UAPs with Explainability against DRL-based IDS (arXiv 2609.30605)</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Venue type</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>preprint only, no journal version found</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Explainable Autonomous Cyber Defense using Adversarial MARL / C-MADF (arXiv 2604.04442)</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Venue type</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>preprint only, no journal version found</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Robust Semi-Supervised Temporal Intrusion Detection (RSST-NIDS) (arXiv 2604.12655)</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Venue type</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>preprint only, no journal version found</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>AOC-IDS: Autonomous Online Framework with Contrastive Learning (arXiv 2402.01807)</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Venue type</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>preprint only, no journal version found</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>HuntGPT: ML anomaly detection + XAI + LLM (arXiv 2309.16021)</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Venue type</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>preprint only, no journal version found</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Continual Learning with Strategic Selection and Forgetting (SSF)</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>IEEE INFOCOM 2025</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Venue type</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>conference paper</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>ExpIDS: Drift-adaptable NIDS with Improved Explainability</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>IEEE conference (Xplore 10815461)</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Venue type</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>conference paper</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Replay or Regret: Evaluating Continual Learning Methods for Robust ID</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>IEEE MILCOM 2025</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Venue type</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>conference paper</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Poster: SCL-IDS Semi-Supervised Continual Learning for Adaptive ID</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>IEEE ICNP 2025</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Venue type</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>poster</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>MAML AE-SAC: Meta-Learning and Adversarial RL for Adaptive ID</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>KSE 2025</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Venue type</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>conference paper</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Q-ID: A Reinforcement Learning Framework for Adaptive Intrusion Detection</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>FedCSIS 2025</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Venue type</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>conference paper</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Deep RL-Based IDS for Next-Generation Wireless Networks</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>ICIRCA 2025</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Venue type</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>conference paper</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Network Anomaly Detection Using Q-Learning and Deep Q-Learning (UNSW-NB15 zero-day)</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>ICSECS 2025</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Venue type</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>conference paper</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Detecting Zero-Day Attacks in Cloud Environments Using Adaptive DQN (ZDADS)</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>ICCES 2025</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Venue type</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>conference paper</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Explainable Graph-based Reinforcement Learning for Intrusion Detection</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>ICCMC 2025</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Venue type</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>conference paper</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Reinforcement Learning for Automated Intrusion Detection in Zero-Day Scenarios</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Book chapter (2025)</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Venue type</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>book chapter</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Online Framework for IDS with explainability-driven drift detector</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>CEUR-WS Vol-4198</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Venue type</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>workshop paper</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Continual Learning for Intrusion Detection Under Evolving Network Threats (Guo et al.)</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Future Internet</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Journal rank</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>journal below Q1 (SJR 2024 Q2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Post-Hoc Categorization Based on XAI and RL for Improved Intrusion Detection</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Applied Sciences</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Journal rank</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>journal below Q1 (SJR 2024 Q2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>A Continual Learning Process to Detect Previously Learned and Newly Emerging Attacks (Memory-LGBM)</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Applied Sciences</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Journal rank</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>journal below Q1 (SJR 2024 Q2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>A versatile XAI-based framework for efficient and explainable IDS</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Annals of Telecommunications</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Journal rank</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>journal below Q1 (SJR 2024 Q2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>SpIDER: Satellite Intrusion Detection Using Explainable Reinforcement Learning</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Telecom (MDPI)</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>not verified</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Journal rank</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>rank not verifiable / not Q1</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Harnessing DBSCAN and auto-encoder for hyper intrusion detection in cloud computing</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Bulletin of Electrical Engineering and Informatics</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>not verified</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Journal rank</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>rank not verifiable / not Q1</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Application of DRL for Intrusion Detection in IoT: A Systematic Review</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Internet of Things (Elsevier)</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Full text</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>review (used for snowballing)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Evolving cybersecurity frontiers: survey on concept drift in IDS</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Engineering Applications of AI</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Full text</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>survey (used for snowballing)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>XAI-Guided Continual Learning: Rationale, Methods, and Future Directions</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>WIREs Data Mining and Knowledge Discovery</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>not verified</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Full text</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>review, outside IDS (evidence that XAI-guided CL exists outside security)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Explaining anomalies detected by autoencoders using SHAP (Antwarg et al.)</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Expert Systems with Applications</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Full text</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>out of domain (not network traffic); methodological enabler for gap 1</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1099,6 +2268,6097 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="55" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Gap</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Closest papers</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>What exists vs what is missing</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>How to claim novelty</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Strength</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>G1</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>XAI-gated pseudo-labels: explanations decide whether an automatically labelled zero-day sample may enter continual retraining</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Afzaal et al. 2026 (confidence + agreement gate); Guo et al. 2025 (entropy + agreement); SOUL, RSST-NIDS (confidence); UNAD+ 2026 (human check, post-hoc LIME); CADE 2021 (explains drift samples for analysts)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>No paper uses explanations to accept or reject pseudo-labels. Every existing gate uses confidence, model agreement or a human.</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Claim: explanation consistency as the admission rule for pseudo-labelled zero-day samples in continual NIDS. Must beat a confidence gate (PseudoFilter) as baseline. Motivation evidence: AOC-IDS 90% -&gt; 75% collapse; GARDIAN on UGRansome (82.5% labels hurt fine-tuning).</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Strong: core contribution</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Explanation-aware DRL controller: a DRL agent uses explanation signals (state or reward) to decide when / how much to retrain a detector, with veto or rollback</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>PARTIALLY ADDRESSED</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>DeepXplain 2026 (explanations in DRL reward / loss); C-MADF 2026 (explainability score gates actions); Drago et al. 2026 and CMC 2023 (SHAP-profile change triggers adaptation, no RL); GARDIAN (DRL retraining control, no XAI)</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Explanation signals inside DRL exist, but only for response actions; XAI-triggered adaptation exists, but without RL.</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Claim must be narrow: a DRL controller for continual retraining of a NIDS whose state includes explanation shift, with skip / rollback actions. Position explicitly against DeepXplain, C-MADF and Drago et al.</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Medium: good extension, not standalone</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>G3</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Explaining continual updates: explanations that show how the detector changes across updates (forgetting, drift impact)</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>PARTIALLY ADDRESSED</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Drago et al. 2026 (explains drift impact and how decisions evolve); CADE 2021 (explains drift samples); CMC 2023 (SHAP drift detection); Explain to Not Forget, WIREs review (XAI against forgetting, outside IDS)</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Explaining drift in NIDS is done. Explaining forgetting caused by each continual update (replay / generated samples) in a NIDS is not.</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Use as an evaluation / analysis component (attribution diff before vs after each update), not as the main novelty.</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Weak as standalone</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>G4</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Encoding vs novelty: how categorical feature encoding affects unsupervised zero-day detectability</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>OPEN (narrow)</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>None. ACORN-IDS, AOC-IDS (one-hot) and ThreatFormer-IDS (embeddings) choose an encoding without studying it; Alkasassbeh et al. label-encode</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>No study of how categorical encoding changes zero-day detectability.</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Supporting experiment: our UGRansome result (label encoding AUC 0.49 vs one-hot 0.94).</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Supporting finding</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Counts over all 63 papers</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>G1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>High overlap: 5, Low overlap: 5, No overlap: 43, Partial overlap: 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>High overlap: 2, Low overlap: 13, No overlap: 45, Partial overlap: 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>G3</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>High overlap: 5, Low overlap: 4, No overlap: 52, Partial overlap: 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>G4</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Low overlap: 2, No overlap: 60, Partial overlap: 1</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:T76"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="9" max="9"/>
+    <col width="32" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="40" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="40" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="40" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="40" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="19" max="19"/>
+    <col width="30" customWidth="1" min="20" max="20"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Venue</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Venue type</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Unsupervised</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>DRL</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Continual / drift</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>XAI</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Related part of your work</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>G1 verdict</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>G1 why</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>G2 verdict</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>G2 why</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>G3 verdict</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>G3 why</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>G4 verdict</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>G4 why</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Extraction source</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>GARDIAN: Deep RL for autonomous and continual network intrusion detection</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>J. Information Security and Applications</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Q1 journal (included)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Baseline framework for your work: unsupervised labelling + DRL + continual learning (no XAI)</t>
+        </is>
+      </c>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>Partial overlap</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Pseudo-labels from MAE + DBSCAN with no quality gate and no XAI; our run: 82.5% correct, harmful for fine-tuning</t>
+        </is>
+      </c>
+      <c r="M2" s="4" t="inlineStr">
+        <is>
+          <t>Partial overlap</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>PPO decides when / how much to retrain, but its state has no explanation signals and it cannot roll back</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>full text</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.jisa.2026.104594</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>A Self-Adaptive IDS for Zero-Day Attacks Using Deep Q-Networks</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>IEEE Access</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Q1 journal (included)</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr"/>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Zero-day ransomware DRL baseline on UGRansome</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q3" s="4" t="inlineStr">
+        <is>
+          <t>Partial overlap</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>Uses label-encoded categoricals without studying encoding; our test shows it hides unseen families (AUC 0.49)</t>
+        </is>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>full text</t>
+        </is>
+      </c>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1109/ACCESS.2025.3617792</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>An active learning framework using deep Q-network for zero-day attack detection</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Computers &amp; Security</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Q1 journal (included)</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>DRL chooses which zero-day samples get labelled</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>Partial overlap</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>DQN selects samples for labelling; labels assigned by distance, never checked with explanations</t>
+        </is>
+      </c>
+      <c r="M4" s="6" t="inlineStr">
+        <is>
+          <t>Low overlap</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>DRL used for sample selection, not to control retraining</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>abstract</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.cose.2024.103713</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Auto-IDaS: RL to configure models, tasks and capacities</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>J. Network and Computer Applications</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Q1 journal (included)</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>DRL as an IDS manager (model selection)</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M5" s="6" t="inlineStr">
+        <is>
+          <t>Low overlap</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>DQN switches detector models over time; no XAI, no retraining decision</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>abstract</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.jnca.2024.103936</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>RL for Intrusion Detection: More Model Longness and Fewer Updates</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>IEEE Trans. Network and Service Management</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Q1 journal (included)</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Long-horizon RL classifier with transfer-learning updates (4 years of real traffic)</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M6" s="6" t="inlineStr">
+        <is>
+          <t>Low overlap</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>Update schedule is periodic; RL does not decide when to update; no XAI</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>full text (partial)</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>https://secplab.ppgia.pucpr.br/files/papers/2023tnsm.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Adaptive Defense: Zero-Day Attack Detection in NIDS with DRL</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>IEEE Access</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Q1 journal (included)</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr"/>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>DRL zero-day baseline with public code</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>abstract</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>https://ieeexplore.ieee.org/document/11063272</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>DQ-IDS: Deep Q-learning intrusion detection system</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>ICT Express</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Q1 journal (included)</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>DRL classifier baseline</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>abstract</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sciencedirect.com/science/article/pii/S2405959525000694</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Cross-dataset zero-day IDS integrating Siamese network and RL</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>ICT Express</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Q1 journal (included)</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Unsupervised detection + PPO; lists XAI as future work</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>Partial overlap</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>Zero-day labels defined by a distance threshold, never validated</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>full text (arXiv version)</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sciencedirect.com/science/article/pii/S2405959526000731</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>ULTIMATE: Multi-agent DRL for false-positive optimized enterprise ID</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Array</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Q1 journal (included)</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>DRL + SHAP example</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M10" s="6" t="inlineStr">
+        <is>
+          <t>Low overlap</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>SHAP explains the agents after the fact; explanations do not drive decisions</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>abstract</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sciencedirect.com/science/article/pii/S2590005626002195</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Adaptive IIoT intrusion detection using DRL against APT attacks (DRL-GCN)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Eng. Applications of AI</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Q1 journal (included)</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>Online DRL policy adaptation under drift</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M11" s="6" t="inlineStr">
+        <is>
+          <t>Low overlap</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>DRL updates its policy online; no explanation signals</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>abstract</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sciencedirect.com/science/article/abs/pii/S0952197626018336</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>IGPC-MSOS: knowledge-preserving mode-switching for concept drift</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Knowledge-Based Systems</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Q1 journal (included)</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>Drift-triggered adaptation baseline</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M12" s="6" t="inlineStr">
+        <is>
+          <t>Low overlap</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>Drift + performance trigger decides adaptation (not RL, not XAI)</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>abstract</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.knosys.2026.115361</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>RL-based voting for feature drift-aware ID (IFDA-GPC)</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>IEEE Access</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Q1 journal (included)</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>DQN feature selection under feature drift</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M13" s="6" t="inlineStr">
+        <is>
+          <t>Low overlap</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>DRL picks features, not retraining; no XAI</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>abstract</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>https://ieeexplore.ieee.org/document/10896652</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Analysis of Continual Learning Models for IDS</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>IEEE Access</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Q1 journal (included)</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Continual-learning baselines (LwF, ER, DER)</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O14" s="6" t="inlineStr">
+        <is>
+          <t>Low overlap</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>Measures forgetting but gives no explanations</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>abstract</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1109/ACCESS.2022.3222715</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>RepShield: robust knowledge representation in CL for NIDS</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Computer Networks</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Q1 journal (included)</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr"/>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>Continual-learning baseline with drift detection</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O15" s="6" t="inlineStr">
+        <is>
+          <t>Low overlap</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>PCA drift detector; no explanations</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>abstract</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sciencedirect.com/science/article/abs/pii/S1389128626003208</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Latent space alignment for IoT botnet detection in non-stationary environments</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Knowledge-Based Systems</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Q1 journal (included)</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr"/>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>Drift robustness without retraining</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>abstract</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sciencedirect.com/science/article/pii/S0950705125017873</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>VLSA-CL: variational latent alignment + contrastive learning under drift</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Neurocomputing</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Q1 journal (included)</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr"/>
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>Drift robustness without retraining</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>abstract</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sciencedirect.com/science/article/pii/S0925231226014967</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>ONIDS: class-imbalance and drift invariant online botnet detection</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Computers &amp; Security</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Q1 journal (included)</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>Online drift-adaptive IoT IDS</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>abstract</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sciencedirect.com/science/article/abs/pii/S0167404824001214</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>An adaptable deep learning-based IDS to zero-day attacks (DOC++)</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>J. Information Security and Applications</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Q1 journal (included)</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>Open-set detection, then clustering of unknown samples for later updates</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>Partial overlap</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>Clusters novel samples so they can be labelled; no explanation-based validation</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>abstract</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.jisa.2023.103516</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Intelligent zero-day attack detection using unsupervised ML (ZdAD-UML)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Knowledge-Based Systems</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Q1 journal (included)</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>Unsupervised zero-day + SHAP</t>
+        </is>
+      </c>
+      <c r="K20" s="6" t="inlineStr">
+        <is>
+          <t>Low overlap</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>SHAP used to explain detections only; no labels, no updates</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>abstract</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.knosys.2025.113833</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Semi-supervised in-vehicle IDS with VAE and adversarial RL</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Knowledge-Based Systems</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Q1 journal (included)</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>Pseudo-labels + RL for unknown attacks</t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>Partial overlap</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>Pseudo-labels for pre-training without an explanation check</t>
+        </is>
+      </c>
+      <c r="M21" s="6" t="inlineStr">
+        <is>
+          <t>Low overlap</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>Adversarial RL agents classify / select samples, not retraining control</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>abstract</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.knosys.2024.112563</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Application of DRL to intrusion detection for supervised problems</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Expert Systems with Applications</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Q1 journal (included)</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr"/>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>Foundational DRL-IDS reference</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>abstract</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>Not retrieved</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>CNN feature extraction + OC-SVM for zero-day detection</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Scientific Reports</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Q1 journal (included)</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr"/>
+      <c r="I23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>One-class zero-day baseline with code</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>full text (PMC)</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC13527146/</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Enhancing Autonomous Online IDS for IoT with Reliable Pseudo-Labels (PseudoFilter)</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>arXiv 2605.26166</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Preprint (arXiv)</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>Closest non-XAI pseudo-label gate: your G1 baseline</t>
+        </is>
+      </c>
+      <c r="K24" s="7" t="inlineStr">
+        <is>
+          <t>High overlap</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>Accepts a pseudo-label only if confidence &gt;= 0.85 AND encoder/decoder agree (+1.25 pts acc); uses no XAI. Also shows AOC-IDS accuracy collapsing 90% -&gt; 75% without a gate</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>full text</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2605.26166</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>SOUL: Semi-supervised Open-world continUal Learning for NIDS</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>arXiv 2412.00911</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Preprint (arXiv)</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>Label-efficient CL baseline (&lt;=20% labels)</t>
+        </is>
+      </c>
+      <c r="K25" s="7" t="inlineStr">
+        <is>
+          <t>High overlap</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>Generates high-confidence labels for new tasks; confidence-based, no XAI</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>abstract</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2412.00911</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>RSST-NIDS: Robust Semi-Supervised Temporal ID for adversarial cloud networks</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>arXiv 2604.12655</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Preprint (arXiv)</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>Confidence-aware pseudo-labelling under drift</t>
+        </is>
+      </c>
+      <c r="K26" s="7" t="inlineStr">
+        <is>
+          <t>High overlap</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>Confidence-aware pseudo-labelling; no XAI</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>abstract</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2604.12655</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>UNAD+: Explainable Hybrid Framework for Unknown Network Attack Detection</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>arXiv 2605.22621</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Preprint (arXiv)</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr"/>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>Unsupervised zero-day -&gt; pseudo-labels -&gt; supervised refinement + LIME</t>
+        </is>
+      </c>
+      <c r="K27" s="7" t="inlineStr">
+        <is>
+          <t>High overlap</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>Pseudo-labels refine a classifier; a HUMAN checks a subset; LIME/surrogate are post hoc and never gate labels</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>full text</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2605.22621</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>ACORN-IDS: Adaptive Continual Novelty Detection for IDS</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>arXiv 2602.07291</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Preprint (arXiv)</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>Continual novelty detection; strong unsupervised-CL baseline (5 datasets)</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>Partial overlap</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>K-Means pseudo-labels from overlap with clean normal data; no gate, no XAI</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q28" s="6" t="inlineStr">
+        <is>
+          <t>Low overlap</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>One-hot encodes categoricals but does not study the effect</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>full text</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2602.07291</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>CITADEL: Continual Anomaly Detection for IoT Intrusion Detection</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>arXiv 2508.19450</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Preprint (arXiv)</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>Self-supervised CL novelty-detection baseline</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>abstract</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2508.19450</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>ThreatFormer-IDS: zero-day generalization and explainable attribution</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>arXiv 2603.00185</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Preprint (arXiv)</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr"/>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>Zero-day + Integrated-Gradients attribution per alert</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O30" s="6" t="inlineStr">
+        <is>
+          <t>Low overlap</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>Explains individual alerts; CL listed as future work</t>
+        </is>
+      </c>
+      <c r="Q30" s="6" t="inlineStr">
+        <is>
+          <t>Low overlap</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>Categorical vocabulary embeddings, not studied</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>full text</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2603.00185</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>DeepXplain: XAI-Guided Autonomous Defense Against Multi-Stage APT</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>arXiv 2603.21296 (under review, GLOBECOM 2026)</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Preprint (arXiv)</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr"/>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr"/>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>Explanation signals inside DRL training: closest to G2</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M31" s="7" t="inlineStr">
+        <is>
+          <t>High overlap</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>Explanation-alignment loss + explanation-confidence reward shape a PPO defence policy. BUT it chooses response actions for APTs, not detector retraining; no CL, no rollback</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>full text</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2603.21296</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>C-MADF: Explainable Autonomous Cyber Defense using Adversarial MARL</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>arXiv 2604.04442</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Preprint (arXiv)</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr"/>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr"/>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>Explainability score gates autonomous actions</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M32" s="7" t="inlineStr">
+        <is>
+          <t>High overlap</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>Explainability-Transparency Score decides escalation vs autonomous action; for response actions, not retraining</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>full text</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2604.04442</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Navigating the Latent Manifold: Proactive Concept Drift Adaptation for NIDS</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>arXiv 2609.08623</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Preprint (arXiv)</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr"/>
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>Drift adaptation related work</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t>abstract</t>
+        </is>
+      </c>
+      <c r="T33" s="2" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2609.08623</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Universal adversarial perturbations with explainability against DRL-based IDS</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>arXiv 2609.30605</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Preprint (arXiv)</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr"/>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr"/>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>Robustness of DRL-IDS</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M34" s="6" t="inlineStr">
+        <is>
+          <t>Low overlap</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>Explains attacks on a DRL-IDS; not adaptation</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>abstract</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2609.30605</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>HuntGPT: ML anomaly detection + XAI + LLM</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>arXiv 2309.16021</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Preprint (arXiv)</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr"/>
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr"/>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>Analyst-facing XAI</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>abstract</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2309.16021</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Explain to Not Forget: Defending Against Catastrophic Forgetting with XAI</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>arXiv 2205.01929 (venue not verified)</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Preprint (arXiv)</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr"/>
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>XAI against forgetting (outside IDS)</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O36" s="7" t="inlineStr">
+        <is>
+          <t>High overlap</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>Uses explanations to reduce forgetting in CL, but on vision tasks, not NIDS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>abstract</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2205.01929</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>CIP-Net: Continual Interpretable Prototype-based Network</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>arXiv 2512.07981</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Preprint (arXiv)</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr"/>
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>Interpretable continual learning (outside IDS)</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O37" s="4" t="inlineStr">
+        <is>
+          <t>Partial overlap</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>Interpretable prototypes in CL; not security</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>abstract</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2512.07981</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>ADAPT: pseudo-labeling to combat concept drift in malware detection</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>arXiv 2507.08597</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Preprint (arXiv)</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr"/>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>Pseudo-labels for drift (malware, not NIDS)</t>
+        </is>
+      </c>
+      <c r="K38" s="4" t="inlineStr">
+        <is>
+          <t>Partial overlap</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>Pseudo-labelling for drift adaptation; no XAI gate in title/abstract</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>title/abstract snippet</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2507.08597</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>AOC-IDS: Autonomous Online Framework with Contrastive Learning</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>IEEE INFOCOM 2024</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Conference / workshop / chapter</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr"/>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>Autonomous online IDS with AE pseudo-labels; code available</t>
+        </is>
+      </c>
+      <c r="K39" s="4" t="inlineStr">
+        <is>
+          <t>Partial overlap</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>Pseudo-labels with no quality gate (only 5% random flips); accuracy collapses over time per Afzaal et al.</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S39" s="2" t="inlineStr">
+        <is>
+          <t>abstract</t>
+        </is>
+      </c>
+      <c r="T39" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/xinchen930/AOC-IDS</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>SSF: Continual Learning with Strategic Selection and Forgetting for NIDS</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>IEEE INFOCOM 2025</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Conference / workshop / chapter</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr"/>
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr"/>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>Strong CL baseline (top-tier venue)</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>abstract</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2412.16264</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Online IDS framework with explainable concept drift detection and adaptation (Drago et al.)</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>ITASEC &amp; SERICS 2026 (CEUR-WS 4198)</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Conference / workshop / chapter</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>Closest to G3; partly G2 (XAI decides when to adapt)</t>
+        </is>
+      </c>
+      <c r="K41" s="6" t="inlineStr">
+        <is>
+          <t>Low overlap</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>Lowers labelling cost by requesting few human labels; no pseudo-label validation</t>
+        </is>
+      </c>
+      <c r="M41" s="4" t="inlineStr">
+        <is>
+          <t>Partial overlap</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>Label-free drift detector based on changes in SHAP feature-importance profiles triggers adaptation; no RL</t>
+        </is>
+      </c>
+      <c r="O41" s="7" t="inlineStr">
+        <is>
+          <t>High overlap</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>Explains the drift's impact and shows how model decisions evolve over time</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>full text</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>https://ceur-ws.org/Vol-4198/paper54.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>ExpIDS: drift-adaptable NIDS with improved explainability</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>IEEE conference (Xplore 10815461)</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Conference / workshop / chapter</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>Drift-adaptive AE with decision-tree explanations</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O42" s="4" t="inlineStr">
+        <is>
+          <t>Partial overlap</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>Global TRUSTEE explanations of the current model; drift updates via U-index with ground-truth labels; does not explain changes between updates</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t>full text</t>
+        </is>
+      </c>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2509.20767</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>CADE: Detecting and Explaining Concept Drift Samples for Security Applications</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>USENIX Security 2021</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Conference / workshop / chapter</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>Explains drifting samples for analysts</t>
+        </is>
+      </c>
+      <c r="K43" s="4" t="inlineStr">
+        <is>
+          <t>Partial overlap</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>Explains why a sample drifted to help analysts label it; no automatic gate</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O43" s="7" t="inlineStr">
+        <is>
+          <t>High overlap</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>Detects and explains concept-drift samples</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>title + citation (ExpIDS ref. 9)</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.usenix.org/conference/usenixsecurity21/presentation/yang-limin</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>ENIDrift: fast adaptive ensemble NIDS under real-world drift</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>ACSAC 2022</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Conference / workshop / chapter</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr"/>
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>Drift-adaptive NIDS baseline</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t>citation (ExpIDS ref. 13)</t>
+        </is>
+      </c>
+      <c r="T44" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1145/3564625.3567992</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Replay or Regret: Evaluating CL Methods for Robust ID</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>IEEE MILCOM 2025</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Conference / workshop / chapter</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr"/>
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr"/>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>Replay is the most effective CL strategy</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O45" s="6" t="inlineStr">
+        <is>
+          <t>Low overlap</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>Measures forgetting, no explanations</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S45" s="2" t="inlineStr">
+        <is>
+          <t>abstract</t>
+        </is>
+      </c>
+      <c r="T45" s="2" t="inlineStr">
+        <is>
+          <t>Not retrieved</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>SCL-IDS: Semi-Supervised Continual Learning for Adaptive ID (poster)</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>IEEE ICNP 2025</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Conference / workshop / chapter</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr"/>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>Semi-supervised CL</t>
+        </is>
+      </c>
+      <c r="K46" s="6" t="inlineStr">
+        <is>
+          <t>Low overlap</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>Semi-supervised CL with scarce labels; no XAI</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>abstract</t>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t>Not retrieved</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>MAML AE-SAC: Meta-Learning and Adversarial RL for Adaptive ID</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>KSE 2025</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Conference / workshop / chapter</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr"/>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr"/>
+      <c r="I47" s="2" t="inlineStr"/>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>Fast-adapting RL IDS</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M47" s="6" t="inlineStr">
+        <is>
+          <t>Low overlap</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>RL adapts quickly; no explanation signals</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S47" s="2" t="inlineStr">
+        <is>
+          <t>abstract</t>
+        </is>
+      </c>
+      <c r="T47" s="2" t="inlineStr">
+        <is>
+          <t>Not retrieved</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Q-ID: RL framework for adaptive intrusion detection</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>FedCSIS 2025</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Conference / workshop / chapter</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr"/>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr"/>
+      <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>RL classifier</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S48" s="2" t="inlineStr">
+        <is>
+          <t>abstract</t>
+        </is>
+      </c>
+      <c r="T48" s="2" t="inlineStr">
+        <is>
+          <t>Not retrieved</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>DRL-based IDS for next-generation wireless networks</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>ICIRCA 2025</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Conference / workshop / chapter</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr"/>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr"/>
+      <c r="I49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>DRL classifier</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S49" s="2" t="inlineStr">
+        <is>
+          <t>abstract</t>
+        </is>
+      </c>
+      <c r="T49" s="2" t="inlineStr">
+        <is>
+          <t>Not retrieved</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Network anomaly detection using Q-Learning and DQN (UNSW-NB15 zero-day)</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>ICSECS 2025</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Conference / workshop / chapter</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr"/>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr"/>
+      <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>DRL zero-day classifier</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S50" s="2" t="inlineStr">
+        <is>
+          <t>abstract</t>
+        </is>
+      </c>
+      <c r="T50" s="2" t="inlineStr">
+        <is>
+          <t>Not retrieved</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>ZDADS: zero-day detection in cloud with adaptive DQN</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>ICCES 2025</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Conference / workshop / chapter</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr"/>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr"/>
+      <c r="I51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>DRL zero-day classifier</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S51" s="2" t="inlineStr">
+        <is>
+          <t>abstract</t>
+        </is>
+      </c>
+      <c r="T51" s="2" t="inlineStr">
+        <is>
+          <t>Not retrieved</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Explainable graph-based RL for intrusion detection</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>ICCMC 2025</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Conference / workshop / chapter</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr"/>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr"/>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>Conceptual XAI + RL</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M52" s="6" t="inlineStr">
+        <is>
+          <t>Low overlap</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>Proposes combining XAI with RL conceptually; no explanation-driven decisions</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S52" s="2" t="inlineStr">
+        <is>
+          <t>abstract</t>
+        </is>
+      </c>
+      <c r="T52" s="2" t="inlineStr">
+        <is>
+          <t>Not retrieved</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>RL for automated ID and adaptive defense in zero-day scenarios (chapter)</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Book chapter</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Conference / workshop / chapter</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr"/>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr"/>
+      <c r="I53" s="2" t="inlineStr"/>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>Background</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S53" s="2" t="inlineStr">
+        <is>
+          <t>abstract</t>
+        </is>
+      </c>
+      <c r="T53" s="2" t="inlineStr">
+        <is>
+          <t>Not retrieved</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Continual Learning for Intrusion Detection Under Evolving Network Threats (Guo et al.)</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Future Internet (Q2)</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Journal below Q1 / rank not verified</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr"/>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>Clustering memory + distillation + pseudo-label filtering</t>
+        </is>
+      </c>
+      <c r="K54" s="7" t="inlineStr">
+        <is>
+          <t>High overlap</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>Confidence-aware pseudo-label filtering (entropy + agreement); no XAI</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S54" s="2" t="inlineStr">
+        <is>
+          <t>abstract</t>
+        </is>
+      </c>
+      <c r="T54" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.3390/fi17100456</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Post-hoc categorization based on XAI and RL for improved ID</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Applied Sciences (Q2)</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Journal below Q1 / rank not verified</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr"/>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr"/>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>Explaining an RL-based IDS</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M55" s="6" t="inlineStr">
+        <is>
+          <t>Low overlap</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>Multi-level post-hoc explanations of an RL classifier</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S55" s="2" t="inlineStr">
+        <is>
+          <t>abstract</t>
+        </is>
+      </c>
+      <c r="T55" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.3390/app142411511</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Continual learning process for learned and emerging attacks (Memory-LGBM)</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Applied Sciences (Q2)</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Journal below Q1 / rank not verified</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr"/>
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr"/>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>Prototype-memory CL baseline</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S56" s="2" t="inlineStr">
+        <is>
+          <t>abstract</t>
+        </is>
+      </c>
+      <c r="T56" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.3390/app151810034</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Versatile XAI-based framework for efficient explainable IDS</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Annals of Telecommunications (Q2)</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Journal below Q1 / rank not verified</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr"/>
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr"/>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>Cost and reliability of XAI (SHAP vs LIME cross-check)</t>
+        </is>
+      </c>
+      <c r="K57" s="6" t="inlineStr">
+        <is>
+          <t>Low overlap</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>Cross-checking two explainers is a reliability test that could serve inside a gate</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S57" s="2" t="inlineStr">
+        <is>
+          <t>abstract</t>
+        </is>
+      </c>
+      <c r="T57" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1007/s12243-025-01118-9</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>SpIDER: satellite ID using explainable RL</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Telecom (MDPI)</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Journal below Q1 / rank not verified</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr"/>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr"/>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>DRL + SHAP example</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M58" s="6" t="inlineStr">
+        <is>
+          <t>Low overlap</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>SHAP explains the RL model post hoc</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S58" s="2" t="inlineStr">
+        <is>
+          <t>abstract</t>
+        </is>
+      </c>
+      <c r="T58" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.3390/telecom7010003</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Harnessing DBSCAN and autoencoder for intrusion detection in cloud</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Bull. Electrical Eng. &amp; Informatics</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Journal below Q1 / rank not verified</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr"/>
+      <c r="I59" s="2" t="inlineStr"/>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>AE detection + DBSCAN clustering of attacks</t>
+        </is>
+      </c>
+      <c r="K59" s="6" t="inlineStr">
+        <is>
+          <t>Low overlap</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>Clusters attacks; no labels for retraining, no XAI</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S59" s="2" t="inlineStr">
+        <is>
+          <t>abstract</t>
+        </is>
+      </c>
+      <c r="T59" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.11591/eei.v13i5.8135</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>XAI-based model drift detection applicable to unsupervised environments</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Computers, Materials &amp; Continua (rank not verified)</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Journal below Q1 / rank not verified</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>SHAP-based drift detection without labels</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M60" s="4" t="inlineStr">
+        <is>
+          <t>Partial overlap</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>Explanations decide when drift occurred; no RL</t>
+        </is>
+      </c>
+      <c r="O60" s="7" t="inlineStr">
+        <is>
+          <t>High overlap</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>Uses SHAP to detect and characterise drift</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S60" s="2" t="inlineStr">
+        <is>
+          <t>abstract</t>
+        </is>
+      </c>
+      <c r="T60" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sciencedirect.com/org/science/article/pii/S1546221823001558</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Application of DRL for intrusion detection in IoT: a systematic review</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Internet of Things (Q1)</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>Review / out of domain</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr"/>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr"/>
+      <c r="I61" s="2" t="inlineStr"/>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>Background on DRL-IDS</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S61" s="2" t="inlineStr">
+        <is>
+          <t>abstract</t>
+        </is>
+      </c>
+      <c r="T61" s="2" t="inlineStr">
+        <is>
+          <t>Not retrieved</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Evolving cybersecurity frontiers: survey on concept drift in IDS</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Eng. Applications of AI (Q1)</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Review / out of domain</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr"/>
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr"/>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>Background on drift</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S62" s="2" t="inlineStr">
+        <is>
+          <t>abstract</t>
+        </is>
+      </c>
+      <c r="T62" s="2" t="inlineStr">
+        <is>
+          <t>Not retrieved</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>XAI-Guided Continual Learning: Rationale, Methods, and Future Directions</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>WIREs Data Mining &amp; Knowledge Discovery</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>Review / out of domain</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr"/>
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>Shows XAI-for-CL exists outside security</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O63" s="7" t="inlineStr">
+        <is>
+          <t>High overlap</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>Reviews XAI used against forgetting (general ML, not IDS)</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S63" s="2" t="inlineStr">
+        <is>
+          <t>abstract</t>
+        </is>
+      </c>
+      <c r="T63" s="2" t="inlineStr">
+        <is>
+          <t>https://wires.onlinelibrary.wiley.com/doi/10.1002/widm.70046</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Explaining anomalies detected by autoencoders using SHAP (Antwarg et al.)</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Expert Systems with Applications (Q1)</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>Review / out of domain</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr"/>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>Method you would build G1 on</t>
+        </is>
+      </c>
+      <c r="K64" s="4" t="inlineStr">
+        <is>
+          <t>Partial overlap</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>Explains AE anomalies with kernel SHAP; no labels or retraining (enabler, not duplicate)</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S64" s="2" t="inlineStr">
+        <is>
+          <t>abstract</t>
+        </is>
+      </c>
+      <c r="T64" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sciencedirect.com/science/article/abs/pii/S0957417421011155</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>Verdict legend</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" s="8" t="inlineStr">
+        <is>
+          <t>Duplicates gap</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>does exactly what the gap proposes</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="9" t="inlineStr">
+        <is>
+          <t>High overlap</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>same core idea in a different setting or with a non-XAI / non-RL substitute</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="10" t="inlineStr">
+        <is>
+          <t>Partial overlap</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>shares one key ingredient</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" s="11" t="inlineStr">
+        <is>
+          <t>Low overlap</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>touches the topic only</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>No overlap</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>not related to this gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>G1</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>XAI-gated pseudo-labels: explanations decide whether an automatically labelled zero-day sample may enter continual retraining</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Explanation-aware DRL controller: a DRL agent uses explanation signals (state or reward) to decide when / how much to retrain a detector, with veto or rollback</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>G3</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Explaining continual updates: explanations that show how the detector changes across updates (forgetting, drift impact)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>G4</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Encoding vs novelty: how categorical feature encoding affects unsupervised zero-day detectability</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:T64"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1763,7 +9023,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2012,7 +9272,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5381,7 +12641,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6982,7 +14242,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7811,7 +15071,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8076,1124 +15336,4 @@
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Research direction</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Addresses gaps</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Motivating papers</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Explanation-gated pseudo-labelling: admit an auto-labelled zero-day sample to retraining only when its attribution profile (SHAP on the autoencoder's reconstruction error, as in Antwarg et al.) agrees with its cluster's profile; report pseudo-label precision.</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Explainability, Label, Method</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>1, 8, 18, 20</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Explanation-aware DRL controller: add attribution-shift features to the agent's state and give it skip / rollback actions, so each retraining decision is justified and harmful updates are vetoed.</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>DRL decision scope, Explainability</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>1, 4, 5, 9</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Explaining continual updates: compare classifier attributions before and after each update to detect forgetting or shortcut learning, and expose it to analysts.</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Explainability, Real-world</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>1, 13, 14</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Novelty-preserving encoding for zero-day ransomware: study categorical encoding (one-hot, embeddings) as a design factor for unsupervised detection, using UGRansome and NetFlow.</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Data / feature representation, Generalization</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>2, 22</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>A shared zero-day continual-learning benchmark protocol: listed held-out families or classes, cross-dataset streams, pseudo-label metrics, multiple seeds, released code.</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Generalization, Statistics / reproducibility</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>1, 2, 5, 8</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E36"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Venue</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Quartile</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Stage</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Reason</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>SOUL: Semi-supervised Open-world continUal Learning for NIDS (arXiv 2412.00911)</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>arXiv</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Venue type</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>preprint only, no journal version found</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>CITADEL: Continual Anomaly Detection for IoT Intrusion Detection (arXiv 2508.19450)</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>arXiv</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Venue type</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>preprint only, no journal version found</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>ACORN-IDS: Adaptive Continual Novelty Detection for IDS (arXiv 2602.07291)</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>arXiv</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Venue type</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>preprint only, no journal version found</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>ThreatFormer-IDS: Zero-Day Generalization and Explainable Attribution (arXiv 2603.00185)</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>arXiv</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Venue type</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>preprint only, no journal version found</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>DeepXplain: XAI-Guided Autonomous Defense Against Multi-Stage APT (arXiv 2603.21296)</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>arXiv</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Venue type</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>preprint only, no journal version found</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>UNAD+: Explainable Hybrid Framework for Unknown Network Attack Detection (arXiv 2605.22621)</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>arXiv</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Venue type</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>preprint only, no journal version found</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Navigating the Latent Manifold: Proactive Concept Drift Adaptation for NIDS (arXiv 2609.08623)</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>arXiv</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Venue type</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>preprint only, no journal version found</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Enhancing Autonomous Online IDS for IoT with Reliable Pseudo-Labels (arXiv 2605.26166)</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>arXiv</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Venue type</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>preprint only, no journal version found</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Probabilistic Robustness-driven UAPs with Explainability against DRL-based IDS (arXiv 2609.30605)</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>arXiv</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Venue type</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>preprint only, no journal version found</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Explainable Autonomous Cyber Defense using Adversarial MARL / C-MADF (arXiv 2604.04442)</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>arXiv</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Venue type</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>preprint only, no journal version found</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Robust Semi-Supervised Temporal Intrusion Detection (RSST-NIDS) (arXiv 2604.12655)</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>arXiv</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Venue type</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>preprint only, no journal version found</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>AOC-IDS: Autonomous Online Framework with Contrastive Learning (arXiv 2402.01807)</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>arXiv</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Venue type</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>preprint only, no journal version found</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>HuntGPT: ML anomaly detection + XAI + LLM (arXiv 2309.16021)</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>arXiv</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Venue type</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>preprint only, no journal version found</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Continual Learning with Strategic Selection and Forgetting (SSF)</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>IEEE INFOCOM 2025</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>Venue type</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>conference paper</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>ExpIDS: Drift-adaptable NIDS with Improved Explainability</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>IEEE conference (Xplore 10815461)</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Venue type</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>conference paper</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Replay or Regret: Evaluating Continual Learning Methods for Robust ID</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>IEEE MILCOM 2025</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Venue type</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>conference paper</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>Poster: SCL-IDS Semi-Supervised Continual Learning for Adaptive ID</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>IEEE ICNP 2025</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Venue type</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>poster</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>MAML AE-SAC: Meta-Learning and Adversarial RL for Adaptive ID</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>KSE 2025</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>Venue type</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>conference paper</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Q-ID: A Reinforcement Learning Framework for Adaptive Intrusion Detection</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>FedCSIS 2025</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>Venue type</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>conference paper</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>Deep RL-Based IDS for Next-Generation Wireless Networks</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>ICIRCA 2025</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>Venue type</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>conference paper</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>Network Anomaly Detection Using Q-Learning and Deep Q-Learning (UNSW-NB15 zero-day)</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>ICSECS 2025</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>Venue type</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>conference paper</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>Detecting Zero-Day Attacks in Cloud Environments Using Adaptive DQN (ZDADS)</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>ICCES 2025</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>Venue type</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>conference paper</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>Explainable Graph-based Reinforcement Learning for Intrusion Detection</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>ICCMC 2025</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>Venue type</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>conference paper</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>Reinforcement Learning for Automated Intrusion Detection in Zero-Day Scenarios</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>Book chapter (2025)</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>Venue type</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>book chapter</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>Online Framework for IDS with explainability-driven drift detector</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>CEUR-WS Vol-4198</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>Venue type</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>workshop paper</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>Continual Learning for Intrusion Detection Under Evolving Network Threats (Guo et al.)</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>Future Internet</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>Q2</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>Journal rank</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>journal below Q1 (SJR 2024 Q2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>Post-Hoc Categorization Based on XAI and RL for Improved Intrusion Detection</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>Applied Sciences</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Q2</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>Journal rank</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>journal below Q1 (SJR 2024 Q2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>A Continual Learning Process to Detect Previously Learned and Newly Emerging Attacks (Memory-LGBM)</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>Applied Sciences</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>Q2</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>Journal rank</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>journal below Q1 (SJR 2024 Q2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>A versatile XAI-based framework for efficient and explainable IDS</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>Annals of Telecommunications</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>Q2</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>Journal rank</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>journal below Q1 (SJR 2024 Q2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>SpIDER: Satellite Intrusion Detection Using Explainable Reinforcement Learning</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>Telecom (MDPI)</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>not verified</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>Journal rank</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>rank not verifiable / not Q1</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>Harnessing DBSCAN and auto-encoder for hyper intrusion detection in cloud computing</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>Bulletin of Electrical Engineering and Informatics</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>not verified</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>Journal rank</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>rank not verifiable / not Q1</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>Application of DRL for Intrusion Detection in IoT: A Systematic Review</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>Internet of Things (Elsevier)</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>Full text</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>review (used for snowballing)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>Evolving cybersecurity frontiers: survey on concept drift in IDS</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>Engineering Applications of AI</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>Full text</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>survey (used for snowballing)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>XAI-Guided Continual Learning: Rationale, Methods, and Future Directions</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>WIREs Data Mining and Knowledge Discovery</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>not verified</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>Full text</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>review, outside IDS (evidence that XAI-guided CL exists outside security)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>Explaining anomalies detected by autoencoders using SHAP (Antwarg et al.)</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>Expert Systems with Applications</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>Full text</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>out of domain (not network traffic); methodological enabler for gap 1</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
-</worksheet>
 </file>